--- a/file/table/DAPC_TamanoPapelNTC1687.xlsx
+++ b/file/table/DAPC_TamanoPapelNTC1687.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5BEF10F-ACBC-419C-9D25-BADD585D47BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B42208-EF79-4FDF-A21F-3C415B0D1E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{805D00DC-0F9A-4825-8987-91294E190814}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t xml:space="preserve">Tamaño de formato de impresión /  Norma técnica Colombiana  NTC-1687 </t>
   </si>
@@ -100,12 +100,6 @@
     <t>Dimensiones (mm)*</t>
   </si>
   <si>
-    <t>Rótulo (mm)</t>
-  </si>
-  <si>
-    <t>Alto**</t>
-  </si>
-  <si>
     <t>La separación de elementos en vistas isométricas es de 25 mm.</t>
   </si>
   <si>
@@ -170,6 +164,9 @@
   </si>
   <si>
     <t>**Tamaño del recuadro de impresión en CAD.</t>
+  </si>
+  <si>
+    <t>Rótulo (mm)**</t>
   </si>
 </sst>
 </file>
@@ -695,7 +692,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -844,9 +841,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1346,7 +1340,7 @@
   <sheetData>
     <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="L1" s="29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
@@ -1376,11 +1370,11 @@
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="30" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J4" s="31"/>
       <c r="K4" s="30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L4" s="31"/>
     </row>
@@ -1398,13 +1392,13 @@
         <v>13</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I5" s="16" t="s">
         <v>15</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K5" s="16" t="s">
         <v>15</v>
@@ -1643,22 +1637,22 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="37" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="37" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="37" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1696,82 +1690,82 @@
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.3">
       <c r="J1" s="29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="2:10" customFormat="1" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="39" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="57"/>
+      <c r="B4" s="56"/>
       <c r="C4" s="52"/>
-      <c r="D4" s="53">
-        <v>180</v>
-      </c>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
+      <c r="D4" s="57">
+        <v>185</v>
+      </c>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
       <c r="J4" s="52"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="57"/>
+      <c r="B5" s="56"/>
       <c r="C5" s="52"/>
-      <c r="D5" s="54">
+      <c r="D5" s="53">
         <v>20</v>
       </c>
-      <c r="E5" s="54">
+      <c r="E5" s="53">
         <v>18</v>
       </c>
-      <c r="F5" s="54">
+      <c r="F5" s="53">
         <v>22</v>
       </c>
-      <c r="G5" s="54">
+      <c r="G5" s="53">
         <v>30</v>
       </c>
-      <c r="H5" s="55">
+      <c r="H5" s="54">
         <f>D4-SUM(D5:G5)</f>
-        <v>90</v>
-      </c>
-      <c r="I5" s="55"/>
+        <v>95</v>
+      </c>
+      <c r="I5" s="54"/>
       <c r="J5" s="52"/>
     </row>
     <row r="6" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="58">
-        <v>36</v>
-      </c>
-      <c r="C6" s="54">
+      <c r="B6" s="57">
+        <v>35</v>
+      </c>
+      <c r="C6" s="53">
         <v>6</v>
       </c>
       <c r="D6" s="41"/>
       <c r="E6" s="41" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G6" s="41" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H6" s="43" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I6" s="44"/>
       <c r="J6" s="52"/>
     </row>
     <row r="7" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="58"/>
-      <c r="C7" s="59">
+      <c r="B7" s="57"/>
+      <c r="C7" s="58">
         <f>C6</f>
         <v>6</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E7" s="41"/>
       <c r="F7" s="41"/>
@@ -1781,13 +1775,13 @@
       <c r="J7" s="52"/>
     </row>
     <row r="8" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="58"/>
-      <c r="C8" s="59">
+      <c r="B8" s="57"/>
+      <c r="C8" s="58">
         <f>C6</f>
         <v>6</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" s="41"/>
       <c r="F8" s="41"/>
@@ -1797,22 +1791,22 @@
       <c r="J8" s="52"/>
     </row>
     <row r="9" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="58"/>
-      <c r="C9" s="60">
+      <c r="B9" s="57"/>
+      <c r="C9" s="59">
         <f>B6-SUM(C6:C8)</f>
-        <v>18</v>
-      </c>
-      <c r="D9" s="61" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="D9" s="60" t="s">
+        <v>26</v>
       </c>
       <c r="E9" s="43" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F9" s="49"/>
       <c r="G9" s="49"/>
       <c r="H9" s="44"/>
       <c r="I9" s="42" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J9" s="52">
         <f>$C$6</f>
@@ -1820,15 +1814,15 @@
       </c>
     </row>
     <row r="10" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="58"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="63"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="62"/>
       <c r="E10" s="45"/>
       <c r="F10" s="50"/>
       <c r="G10" s="50"/>
       <c r="H10" s="46"/>
       <c r="I10" s="42" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J10" s="52">
         <f t="shared" ref="J10:J11" si="0">$C$6</f>
@@ -1836,15 +1830,15 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="58"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="62"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="61"/>
       <c r="E11" s="47"/>
       <c r="F11" s="51"/>
       <c r="G11" s="51"/>
       <c r="H11" s="48"/>
       <c r="I11" s="42" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J11" s="52">
         <f t="shared" si="0"/>
@@ -1852,26 +1846,26 @@
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="57"/>
+      <c r="B12" s="56"/>
       <c r="C12" s="52"/>
       <c r="D12" s="52">
         <f>D5</f>
         <v>20</v>
       </c>
-      <c r="E12" s="56">
+      <c r="E12" s="55">
         <f>D4-I12-D12</f>
-        <v>100</v>
-      </c>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="54">
+        <v>105</v>
+      </c>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="53">
         <v>60</v>
       </c>
       <c r="J12" s="52"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="57"/>
+      <c r="B13" s="56"/>
       <c r="C13" s="52"/>
       <c r="D13" s="52"/>
       <c r="E13" s="52"/>
@@ -1879,7 +1873,7 @@
       <c r="G13" s="52"/>
       <c r="H13" s="52">
         <f>H5-I12</f>
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I13" s="52"/>
       <c r="J13" s="52"/>
@@ -1911,17 +1905,17 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B3" s="63" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B3" s="64" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B4" s="28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/file/table/DAPC_TamanoPapelNTC1687.xlsx
+++ b/file/table/DAPC_TamanoPapelNTC1687.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B42208-EF79-4FDF-A21F-3C415B0D1E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5635DE60-7701-4772-9607-A67305F4AA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{805D00DC-0F9A-4825-8987-91294E190814}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{805D00DC-0F9A-4825-8987-91294E190814}"/>
   </bookViews>
   <sheets>
     <sheet name="NTC1687" sheetId="1" r:id="rId1"/>
@@ -1737,7 +1737,7 @@
     </row>
     <row r="6" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="57">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" s="53">
         <v>6</v>
@@ -1794,7 +1794,7 @@
       <c r="B9" s="57"/>
       <c r="C9" s="59">
         <f>B6-SUM(C6:C8)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" s="60" t="s">
         <v>26</v>

--- a/file/table/DAPC_TamanoPapelNTC1687.xlsx
+++ b/file/table/DAPC_TamanoPapelNTC1687.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5635DE60-7701-4772-9607-A67305F4AA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01E1B82-070C-44E8-A212-927890ACCAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{805D00DC-0F9A-4825-8987-91294E190814}"/>
   </bookViews>
@@ -173,7 +173,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,13 +200,7 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
@@ -214,17 +208,6 @@
     <font>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -239,6 +222,17 @@
     <font>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -690,7 +684,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -810,63 +804,64 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -875,10 +870,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -957,13 +951,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3324501</xdr:colOff>
+      <xdr:colOff>3431181</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>2</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>159729</xdr:colOff>
+      <xdr:colOff>266409</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>55423</xdr:rowOff>
     </xdr:to>
@@ -994,7 +988,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12506601" y="213362"/>
+          <a:off x="12613281" y="213362"/>
           <a:ext cx="1003368" cy="238301"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1678,13 +1672,13 @@
   <cols>
     <col min="1" max="1" width="2.77734375" style="38" customWidth="1"/>
     <col min="2" max="2" width="4.44140625" style="38" customWidth="1"/>
-    <col min="3" max="3" width="2.77734375" style="40" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" style="40" customWidth="1"/>
     <col min="4" max="4" width="20.77734375" style="40" customWidth="1"/>
     <col min="5" max="5" width="18.77734375" style="40" customWidth="1"/>
     <col min="6" max="6" width="22.77734375" style="40" customWidth="1"/>
     <col min="7" max="8" width="30.77734375" style="40" customWidth="1"/>
     <col min="9" max="9" width="60.77734375" style="40" customWidth="1"/>
-    <col min="10" max="10" width="2.77734375" style="40" customWidth="1"/>
+    <col min="10" max="10" width="4.5546875" style="40" customWidth="1"/>
     <col min="11" max="16384" width="8.88671875" style="38"/>
   </cols>
   <sheetData>
@@ -1700,183 +1694,183 @@
       </c>
       <c r="I3" s="29"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="56"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="57">
+    <row r="4" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="54">
         <v>185</v>
       </c>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="52"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="56"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="53">
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="53"/>
+    </row>
+    <row r="5" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B5" s="52"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="55">
         <v>20</v>
       </c>
-      <c r="E5" s="53">
+      <c r="E5" s="55">
         <v>18</v>
       </c>
-      <c r="F5" s="53">
+      <c r="F5" s="55">
         <v>22</v>
       </c>
-      <c r="G5" s="53">
+      <c r="G5" s="55">
         <v>30</v>
       </c>
-      <c r="H5" s="54">
+      <c r="H5" s="56">
         <f>D4-SUM(D5:G5)</f>
         <v>95</v>
       </c>
-      <c r="I5" s="54"/>
-      <c r="J5" s="52"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="57">
+      <c r="B6" s="54">
         <v>36</v>
       </c>
-      <c r="C6" s="53">
+      <c r="C6" s="55">
         <v>6</v>
       </c>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41" t="s">
+      <c r="D6" s="57"/>
+      <c r="E6" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="41" t="s">
+      <c r="G6" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="43" t="s">
+      <c r="H6" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="52"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="57"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="58">
         <f>C6</f>
         <v>6</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="D7" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="52"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="53"/>
     </row>
     <row r="8" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="57"/>
+      <c r="B8" s="54"/>
       <c r="C8" s="58">
         <f>C6</f>
         <v>6</v>
       </c>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="52"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="57"/>
-      <c r="C9" s="59">
+      <c r="B9" s="54"/>
+      <c r="C9" s="60">
         <f>B6-SUM(C6:C8)</f>
         <v>18</v>
       </c>
-      <c r="D9" s="60" t="s">
+      <c r="D9" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="42" t="s">
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="J9" s="52">
+      <c r="J9" s="53">
         <f>$C$6</f>
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="57"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="42" t="s">
+      <c r="B10" s="54"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="52">
+      <c r="J10" s="53">
         <f t="shared" ref="J10:J11" si="0">$C$6</f>
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="57"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="42" t="s">
+      <c r="B11" s="54"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="J11" s="52">
+      <c r="J11" s="53">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="56"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52">
+    <row r="12" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B12" s="52"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53">
         <f>D5</f>
         <v>20</v>
       </c>
-      <c r="E12" s="55">
+      <c r="E12" s="63">
         <f>D4-I12-D12</f>
         <v>105</v>
       </c>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="53">
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="55">
         <v>60</v>
       </c>
-      <c r="J12" s="52"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="56"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52">
+      <c r="J12" s="53"/>
+    </row>
+    <row r="13" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B13" s="52"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53">
         <f>H5-I12</f>
         <v>35</v>
       </c>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1909,7 +1903,7 @@
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="51" t="s">
         <v>39</v>
       </c>
     </row>

--- a/file/table/DAPC_TamanoPapelNTC1687.xlsx
+++ b/file/table/DAPC_TamanoPapelNTC1687.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01E1B82-070C-44E8-A212-927890ACCAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429D802E-F899-4E27-983A-1AECC3606862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{805D00DC-0F9A-4825-8987-91294E190814}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{805D00DC-0F9A-4825-8987-91294E190814}"/>
   </bookViews>
   <sheets>
     <sheet name="NTC1687" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
   <si>
     <t xml:space="preserve">Tamaño de formato de impresión /  Norma técnica Colombiana  NTC-1687 </t>
   </si>
@@ -167,6 +167,12 @@
   </si>
   <si>
     <t>Rótulo (mm)**</t>
+  </si>
+  <si>
+    <t>Rótulo papel A4 - Formato vertical</t>
+  </si>
+  <si>
+    <t>Rótulo papel A4 - Formato horizontal</t>
   </si>
 </sst>
 </file>
@@ -959,7 +965,7 @@
       <xdr:col>9</xdr:col>
       <xdr:colOff>266409</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>55423</xdr:rowOff>
+      <xdr:rowOff>24943</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1667,7 +1673,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385124FB-3544-4512-BFA2-E5E9A28D1AEA}">
-  <dimension ref="B1:J13"/>
+  <dimension ref="B1:J25"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.77734375" style="38" customWidth="1"/>
@@ -1687,10 +1693,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="2:10" customFormat="1" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="39" t="s">
+        <v>34</v>
+      </c>
+    </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="39" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I3" s="29"/>
     </row>
@@ -1872,8 +1882,199 @@
       <c r="I13" s="53"/>
       <c r="J13" s="53"/>
     </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" s="29"/>
+    </row>
+    <row r="16" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B16" s="52"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="54">
+        <v>210</v>
+      </c>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="53"/>
+    </row>
+    <row r="17" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B17" s="52"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="55">
+        <v>20</v>
+      </c>
+      <c r="E17" s="55">
+        <v>18</v>
+      </c>
+      <c r="F17" s="55">
+        <v>22</v>
+      </c>
+      <c r="G17" s="55">
+        <v>30</v>
+      </c>
+      <c r="H17" s="56">
+        <f>D16-SUM(D17:G17)</f>
+        <v>120</v>
+      </c>
+      <c r="I17" s="56"/>
+      <c r="J17" s="53"/>
+    </row>
+    <row r="18" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B18" s="54">
+        <v>36</v>
+      </c>
+      <c r="C18" s="55">
+        <v>6</v>
+      </c>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="42"/>
+      <c r="J18" s="53"/>
+    </row>
+    <row r="19" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B19" s="54"/>
+      <c r="C19" s="58">
+        <f>C18</f>
+        <v>6</v>
+      </c>
+      <c r="D19" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="53"/>
+    </row>
+    <row r="20" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B20" s="54"/>
+      <c r="C20" s="58">
+        <f>C18</f>
+        <v>6</v>
+      </c>
+      <c r="D20" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="53"/>
+    </row>
+    <row r="21" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B21" s="54"/>
+      <c r="C21" s="60">
+        <f>B18-SUM(C18:C20)</f>
+        <v>18</v>
+      </c>
+      <c r="D21" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="59" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="53">
+        <f>$C$6</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B22" s="54"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" s="53">
+        <f t="shared" ref="J22:J23" si="1">$C$6</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B23" s="54"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="59" t="s">
+        <v>29</v>
+      </c>
+      <c r="J23" s="53">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B24" s="52"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53">
+        <f>D17</f>
+        <v>20</v>
+      </c>
+      <c r="E24" s="63">
+        <f>D16-I24-D24</f>
+        <v>130</v>
+      </c>
+      <c r="F24" s="63"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="55">
+        <v>60</v>
+      </c>
+      <c r="J24" s="53"/>
+    </row>
+    <row r="25" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B25" s="52"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53">
+        <f>H17-I24</f>
+        <v>60</v>
+      </c>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="14">
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="B18:B23"/>
+    <mergeCell ref="H18:I20"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:H23"/>
     <mergeCell ref="D4:I4"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="E9:H11"/>

--- a/file/table/DAPC_TamanoPapelNTC1687.xlsx
+++ b/file/table/DAPC_TamanoPapelNTC1687.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429D802E-F899-4E27-983A-1AECC3606862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C93C934-A6EE-4E79-B9F8-1C9BCEDC8738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{805D00DC-0F9A-4825-8987-91294E190814}"/>
   </bookViews>

--- a/file/table/DAPC_TamanoPapelNTC1687.xlsx
+++ b/file/table/DAPC_TamanoPapelNTC1687.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C93C934-A6EE-4E79-B9F8-1C9BCEDC8738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E349DA-EF8A-4791-B35F-F5C01E0CFDDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{805D00DC-0F9A-4825-8987-91294E190814}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="46">
   <si>
     <t xml:space="preserve">Tamaño de formato de impresión /  Norma técnica Colombiana  NTC-1687 </t>
   </si>
@@ -82,9 +82,6 @@
     <t>Izq.</t>
   </si>
   <si>
-    <t>Márgenes (mm)</t>
-  </si>
-  <si>
     <t>Largo</t>
   </si>
   <si>
@@ -160,9 +157,6 @@
     <t>https://tienda.icontec.org/gp-ntc-dibujo-tecnico-formato-y-plegado-de-planos-tecnicos-ntc1687-2023.html</t>
   </si>
   <si>
-    <t>MView CAD (mm) ***</t>
-  </si>
-  <si>
     <t>**Tamaño del recuadro de impresión en CAD.</t>
   </si>
   <si>
@@ -173,6 +167,15 @@
   </si>
   <si>
     <t>Rótulo papel A4 - Formato horizontal</t>
+  </si>
+  <si>
+    <t>MView horizontal CAD (mm) ***</t>
+  </si>
+  <si>
+    <t>MView veritical CAD (mm) ***</t>
+  </si>
+  <si>
+    <t>Márgenes y origen de dibujo CAD (mm)</t>
   </si>
 </sst>
 </file>
@@ -263,7 +266,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -684,6 +687,17 @@
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -692,7 +706,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -710,31 +724,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -742,16 +744,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -761,28 +757,16 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -808,33 +792,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="4" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -851,6 +808,51 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -858,26 +860,59 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -899,25 +934,20 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>396663</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>149670</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>155699</xdr:rowOff>
+      <xdr:rowOff>166209</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>690419</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>180640</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="1003204" cy="240403"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1">
+        <xdr:cNvPr id="3" name="Graphic 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A6D2FA3-C5CF-48CD-959E-8F7FF1DD7A64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{249D17A7-CFF7-4473-8FD0-BE9363697771}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -939,8 +969,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6021176" y="155699"/>
-          <a:ext cx="1003368" cy="239254"/>
+          <a:off x="6965629" y="166209"/>
+          <a:ext cx="1003204" cy="240403"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -948,7 +978,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1324,7 +1354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78567822-AC51-4E36-B21F-DB5ADDD5BD5E}">
-  <dimension ref="B1:L15"/>
+  <dimension ref="B1:N15"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.77734375" style="2" customWidth="1"/>
@@ -1332,89 +1362,101 @@
     <col min="3" max="3" width="10.77734375" style="2" customWidth="1"/>
     <col min="4" max="4" width="10.5546875" style="2" customWidth="1"/>
     <col min="5" max="6" width="10" style="2" customWidth="1"/>
-    <col min="7" max="8" width="7.6640625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="10.21875" style="2" customWidth="1"/>
     <col min="9" max="10" width="6.88671875" style="2" customWidth="1"/>
-    <col min="11" max="12" width="10.33203125" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="2"/>
+    <col min="11" max="14" width="8.5546875" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="L1" s="29" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="L2" s="29"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="L1" s="21"/>
+      <c r="N1" s="21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="L2" s="21"/>
+      <c r="N2" s="21"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="24" t="s">
+    <row r="4" spans="2:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="18" t="s">
+      <c r="F4" s="47"/>
+      <c r="G4" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="70"/>
+      <c r="I4" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="65"/>
+      <c r="K4" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="70"/>
+      <c r="M4" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="N4" s="63"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B5" s="43"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="31"/>
-      <c r="K4" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" s="31"/>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="25"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="16" t="s">
+      <c r="F5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="16" t="s">
+      <c r="H5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="L5" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="26" t="s">
+      <c r="M5" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B6" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="16">
         <v>1</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="10">
         <f>E6*F6/1000000</f>
         <v>0.99994899999999998</v>
       </c>
@@ -1424,36 +1466,44 @@
       <c r="F6" s="4">
         <v>841</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="22">
         <v>20</v>
       </c>
       <c r="H6" s="3">
         <v>10</v>
       </c>
-      <c r="I6" s="32">
+      <c r="I6" s="22">
         <v>180</v>
       </c>
-      <c r="J6" s="33">
+      <c r="J6" s="66">
         <v>35</v>
       </c>
-      <c r="K6" s="32">
-        <f>E6-G6-H6</f>
+      <c r="K6" s="22">
+        <f t="shared" ref="K6:K11" si="0">E6-G6-H6</f>
         <v>1159</v>
       </c>
-      <c r="L6" s="33">
+      <c r="L6" s="3">
         <f>F6-H6-H6</f>
         <v>821</v>
       </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="26" t="s">
+      <c r="M6" s="68">
+        <f>E6-H6-H6</f>
+        <v>1169</v>
+      </c>
+      <c r="N6" s="23">
+        <f>F6-G6-H6</f>
+        <v>811</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B7" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="13">
-        <f t="shared" ref="D7:D11" si="0">E7*F7/1000000</f>
+      <c r="D7" s="10">
+        <f t="shared" ref="D7:D11" si="1">E7*F7/1000000</f>
         <v>0.499554</v>
       </c>
       <c r="E7" s="5">
@@ -1462,36 +1512,44 @@
       <c r="F7" s="4">
         <v>594</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="22">
         <v>20</v>
       </c>
       <c r="H7" s="3">
         <v>10</v>
       </c>
-      <c r="I7" s="32">
+      <c r="I7" s="22">
         <v>180</v>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="66">
         <v>35</v>
       </c>
-      <c r="K7" s="32">
-        <f>E7-G7-H7</f>
+      <c r="K7" s="22">
+        <f t="shared" si="0"/>
         <v>811</v>
       </c>
-      <c r="L7" s="33">
-        <f t="shared" ref="L7:L11" si="1">F7-H7-H7</f>
+      <c r="L7" s="3">
+        <f t="shared" ref="L7:L11" si="2">F7-H7-H7</f>
         <v>574</v>
       </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="26" t="s">
+      <c r="M7" s="68">
+        <f t="shared" ref="M7:M11" si="3">E7-H7-H7</f>
+        <v>821</v>
+      </c>
+      <c r="N7" s="23">
+        <f t="shared" ref="N7:N11" si="4">F7-G7-H7</f>
+        <v>564</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B8" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="13">
-        <f t="shared" si="0"/>
+      <c r="D8" s="10">
+        <f t="shared" si="1"/>
         <v>0.24948000000000001</v>
       </c>
       <c r="E8" s="5">
@@ -1500,36 +1558,44 @@
       <c r="F8" s="4">
         <v>420</v>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="22">
         <v>20</v>
       </c>
       <c r="H8" s="3">
         <v>10</v>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="22">
         <v>180</v>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="66">
         <v>35</v>
       </c>
-      <c r="K8" s="32">
-        <f>E8-G8-H8</f>
+      <c r="K8" s="22">
+        <f t="shared" si="0"/>
         <v>564</v>
       </c>
-      <c r="L8" s="33">
+      <c r="L8" s="3">
+        <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+      <c r="M8" s="68">
+        <f t="shared" si="3"/>
+        <v>574</v>
+      </c>
+      <c r="N8" s="23">
+        <f t="shared" si="4"/>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="10">
         <f t="shared" si="1"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="13">
-        <f t="shared" si="0"/>
         <v>0.12474</v>
       </c>
       <c r="E9" s="5">
@@ -1538,36 +1604,44 @@
       <c r="F9" s="4">
         <v>297</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="22">
         <v>20</v>
       </c>
       <c r="H9" s="3">
         <v>5</v>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="22">
         <v>180</v>
       </c>
-      <c r="J9" s="33">
+      <c r="J9" s="66">
         <v>35</v>
       </c>
-      <c r="K9" s="32">
-        <f>E9-G9-H9</f>
+      <c r="K9" s="22">
+        <f t="shared" si="0"/>
         <v>395</v>
       </c>
-      <c r="L9" s="33">
+      <c r="L9" s="3">
+        <f t="shared" si="2"/>
+        <v>287</v>
+      </c>
+      <c r="M9" s="68">
+        <f t="shared" si="3"/>
+        <v>410</v>
+      </c>
+      <c r="N9" s="23">
+        <f t="shared" si="4"/>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B10" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="10">
         <f t="shared" si="1"/>
-        <v>287</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="13">
-        <f t="shared" si="0"/>
         <v>6.2370000000000002E-2</v>
       </c>
       <c r="E10" s="5">
@@ -1576,90 +1650,107 @@
       <c r="F10" s="4">
         <v>210</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="22">
         <v>20</v>
       </c>
       <c r="H10" s="3">
         <v>5</v>
       </c>
-      <c r="I10" s="32">
+      <c r="I10" s="22">
         <v>180</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J10" s="66">
         <v>35</v>
       </c>
-      <c r="K10" s="32">
-        <f>E10-G10-H10</f>
+      <c r="K10" s="22">
+        <f t="shared" si="0"/>
         <v>272</v>
       </c>
-      <c r="L10" s="33">
+      <c r="L10" s="3">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+      <c r="M10" s="68">
+        <f t="shared" si="3"/>
+        <v>287</v>
+      </c>
+      <c r="N10" s="23">
+        <f t="shared" si="4"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B11" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="11">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="14">
-        <f t="shared" si="0"/>
         <v>3.108E-2</v>
       </c>
       <c r="E11" s="6">
         <v>210</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="13">
         <v>148</v>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="24">
         <v>20</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="25">
         <v>5</v>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="24">
         <v>180</v>
       </c>
-      <c r="J11" s="36">
+      <c r="J11" s="67">
         <v>35</v>
       </c>
-      <c r="K11" s="34">
-        <f>E11-G11-H11</f>
+      <c r="K11" s="24">
+        <f t="shared" si="0"/>
         <v>185</v>
       </c>
-      <c r="L11" s="36">
-        <f t="shared" si="1"/>
+      <c r="L11" s="25">
+        <f t="shared" si="2"/>
         <v>138</v>
       </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="37" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="37" t="s">
+      <c r="M11" s="69">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="N11" s="26">
+        <f t="shared" si="4"/>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B12" s="27" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="37" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="37" t="s">
-        <v>20</v>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B13" s="27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B14" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B15" s="27" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="K4:L4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="E4:F4"/>
@@ -1667,6 +1758,9 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="L6:L11" formula="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -1676,398 +1770,405 @@
   <dimension ref="B1:J25"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.77734375" style="38" customWidth="1"/>
-    <col min="2" max="2" width="4.44140625" style="38" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" style="40" customWidth="1"/>
-    <col min="4" max="4" width="20.77734375" style="40" customWidth="1"/>
-    <col min="5" max="5" width="18.77734375" style="40" customWidth="1"/>
-    <col min="6" max="6" width="22.77734375" style="40" customWidth="1"/>
-    <col min="7" max="8" width="30.77734375" style="40" customWidth="1"/>
-    <col min="9" max="9" width="60.77734375" style="40" customWidth="1"/>
-    <col min="10" max="10" width="4.5546875" style="40" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="38"/>
+    <col min="1" max="1" width="2.77734375" style="28" customWidth="1"/>
+    <col min="2" max="2" width="4.44140625" style="28" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" style="30" customWidth="1"/>
+    <col min="4" max="4" width="20.77734375" style="30" customWidth="1"/>
+    <col min="5" max="5" width="18.77734375" style="30" customWidth="1"/>
+    <col min="6" max="6" width="22.77734375" style="30" customWidth="1"/>
+    <col min="7" max="8" width="30.77734375" style="30" customWidth="1"/>
+    <col min="9" max="9" width="60.77734375" style="30" customWidth="1"/>
+    <col min="10" max="10" width="4.5546875" style="30" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="J1" s="29" t="s">
-        <v>21</v>
+      <c r="J1" s="21" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="39" t="s">
-        <v>34</v>
+      <c r="B2" s="29" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" s="29"/>
+      <c r="B3" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="21"/>
     </row>
     <row r="4" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="54">
+      <c r="B4" s="33"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="51">
         <v>185</v>
       </c>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="53"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="34"/>
     </row>
     <row r="5" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B5" s="52"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="55">
+      <c r="B5" s="33"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="35">
         <v>20</v>
       </c>
-      <c r="E5" s="55">
+      <c r="E5" s="35">
         <v>18</v>
       </c>
-      <c r="F5" s="55">
+      <c r="F5" s="35">
         <v>22</v>
       </c>
-      <c r="G5" s="55">
+      <c r="G5" s="35">
         <v>30</v>
       </c>
-      <c r="H5" s="56">
+      <c r="H5" s="52">
         <f>D4-SUM(D5:G5)</f>
         <v>95</v>
       </c>
-      <c r="I5" s="56"/>
-      <c r="J5" s="53"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="34"/>
     </row>
     <row r="6" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="54">
+      <c r="B6" s="51">
         <v>36</v>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="35">
         <v>6</v>
       </c>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="57" t="s">
+      <c r="D6" s="37"/>
+      <c r="E6" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="42"/>
-      <c r="J6" s="53"/>
+      <c r="G6" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="54"/>
+      <c r="J6" s="34"/>
     </row>
     <row r="7" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="54"/>
-      <c r="C7" s="58">
+      <c r="B7" s="51"/>
+      <c r="C7" s="36">
         <f>C6</f>
         <v>6</v>
       </c>
-      <c r="D7" s="59" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="53"/>
+      <c r="D7" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="34"/>
     </row>
     <row r="8" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="54"/>
-      <c r="C8" s="58">
+      <c r="B8" s="51"/>
+      <c r="C8" s="36">
         <f>C6</f>
         <v>6</v>
       </c>
-      <c r="D8" s="59" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="53"/>
+      <c r="D8" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="34"/>
     </row>
     <row r="9" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="54"/>
-      <c r="C9" s="60">
+      <c r="B9" s="51"/>
+      <c r="C9" s="59">
         <f>B6-SUM(C6:C8)</f>
         <v>18</v>
       </c>
-      <c r="D9" s="61" t="s">
+      <c r="D9" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="59" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" s="53">
+      <c r="J9" s="34">
         <f>$C$6</f>
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="54"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="53">
+      <c r="B10" s="51"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="34">
         <f t="shared" ref="J10:J11" si="0">$C$6</f>
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="54"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="59" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="53">
+      <c r="B11" s="51"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="34">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B12" s="52"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53">
+      <c r="B12" s="33"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34">
         <f>D5</f>
         <v>20</v>
       </c>
-      <c r="E12" s="63">
+      <c r="E12" s="50">
         <f>D4-I12-D12</f>
         <v>105</v>
       </c>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="55">
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="35">
         <v>60</v>
       </c>
-      <c r="J12" s="53"/>
+      <c r="J12" s="34"/>
     </row>
     <row r="13" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B13" s="52"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53">
+      <c r="B13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34">
         <f>H5-I12</f>
         <v>35</v>
       </c>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="29"/>
+      <c r="B15" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="21"/>
     </row>
     <row r="16" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B16" s="52"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="54">
+      <c r="B16" s="33"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="51">
         <v>210</v>
       </c>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="53"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="34"/>
     </row>
     <row r="17" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B17" s="52"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="55">
+      <c r="B17" s="33"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="35">
         <v>20</v>
       </c>
-      <c r="E17" s="55">
+      <c r="E17" s="35">
         <v>18</v>
       </c>
-      <c r="F17" s="55">
+      <c r="F17" s="35">
         <v>22</v>
       </c>
-      <c r="G17" s="55">
+      <c r="G17" s="35">
         <v>30</v>
       </c>
-      <c r="H17" s="56">
+      <c r="H17" s="52">
         <f>D16-SUM(D17:G17)</f>
         <v>120</v>
       </c>
-      <c r="I17" s="56"/>
-      <c r="J17" s="53"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="34"/>
     </row>
     <row r="18" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B18" s="54">
+      <c r="B18" s="51">
         <v>36</v>
       </c>
-      <c r="C18" s="55">
+      <c r="C18" s="35">
         <v>6</v>
       </c>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="57" t="s">
+      <c r="D18" s="37"/>
+      <c r="E18" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="H18" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="42"/>
-      <c r="J18" s="53"/>
+      <c r="G18" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="54"/>
+      <c r="J18" s="34"/>
     </row>
     <row r="19" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B19" s="54"/>
-      <c r="C19" s="58">
+      <c r="B19" s="51"/>
+      <c r="C19" s="36">
         <f>C18</f>
         <v>6</v>
       </c>
-      <c r="D19" s="59" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="53"/>
+      <c r="D19" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="34"/>
     </row>
     <row r="20" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B20" s="54"/>
-      <c r="C20" s="58">
+      <c r="B20" s="51"/>
+      <c r="C20" s="36">
         <f>C18</f>
         <v>6</v>
       </c>
-      <c r="D20" s="59" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="53"/>
+      <c r="D20" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="34"/>
     </row>
     <row r="21" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B21" s="54"/>
-      <c r="C21" s="60">
+      <c r="B21" s="51"/>
+      <c r="C21" s="59">
         <f>B18-SUM(C18:C20)</f>
         <v>18</v>
       </c>
-      <c r="D21" s="61" t="s">
+      <c r="D21" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="59" t="s">
-        <v>27</v>
-      </c>
-      <c r="J21" s="53">
+      <c r="J21" s="34">
         <f>$C$6</f>
         <v>6</v>
       </c>
     </row>
     <row r="22" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B22" s="54"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="J22" s="53">
+      <c r="B22" s="51"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" s="34">
         <f t="shared" ref="J22:J23" si="1">$C$6</f>
         <v>6</v>
       </c>
     </row>
     <row r="23" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B23" s="54"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="59" t="s">
-        <v>29</v>
-      </c>
-      <c r="J23" s="53">
+      <c r="B23" s="51"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="34">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
     <row r="24" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B24" s="52"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53">
+      <c r="B24" s="33"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34">
         <f>D17</f>
         <v>20</v>
       </c>
-      <c r="E24" s="63">
+      <c r="E24" s="50">
         <f>D16-I24-D24</f>
         <v>130</v>
       </c>
-      <c r="F24" s="63"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="55">
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="35">
         <v>60</v>
       </c>
-      <c r="J24" s="53"/>
+      <c r="J24" s="34"/>
     </row>
     <row r="25" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B25" s="52"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="53"/>
-      <c r="H25" s="53">
+      <c r="B25" s="33"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34">
         <f>H17-I24</f>
         <v>60</v>
       </c>
-      <c r="I25" s="53"/>
-      <c r="J25" s="53"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B6:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="E9:H11"/>
+    <mergeCell ref="H6:I8"/>
+    <mergeCell ref="E12:H12"/>
     <mergeCell ref="E24:H24"/>
     <mergeCell ref="D16:I16"/>
     <mergeCell ref="H17:I17"/>
@@ -2075,13 +2176,6 @@
     <mergeCell ref="H18:I20"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="E21:H23"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="E9:H11"/>
-    <mergeCell ref="H6:I8"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="B6:B11"/>
-    <mergeCell ref="C9:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2100,17 +2194,17 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B3" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B4" s="20" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B3" s="51" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B4" s="28" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/file/table/DAPC_TamanoPapelNTC1687.xlsx
+++ b/file/table/DAPC_TamanoPapelNTC1687.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E349DA-EF8A-4791-B35F-F5C01E0CFDDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6407CE0C-3A25-4DAF-91B9-32BD5A239254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{805D00DC-0F9A-4825-8987-91294E190814}"/>
   </bookViews>

--- a/file/table/DAPC_TamanoPapelNTC1687.xlsx
+++ b/file/table/DAPC_TamanoPapelNTC1687.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6407CE0C-3A25-4DAF-91B9-32BD5A239254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E98165-EB09-4080-A199-80CEFC857638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{805D00DC-0F9A-4825-8987-91294E190814}"/>
   </bookViews>

--- a/file/table/DAPC_TamanoPapelNTC1687.xlsx
+++ b/file/table/DAPC_TamanoPapelNTC1687.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E98165-EB09-4080-A199-80CEFC857638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED6EE0A-CC28-4A8E-A628-0BCF69F37FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{805D00DC-0F9A-4825-8987-91294E190814}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{805D00DC-0F9A-4825-8987-91294E190814}"/>
   </bookViews>
   <sheets>
     <sheet name="NTC1687" sheetId="1" r:id="rId1"/>
@@ -823,9 +823,36 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -838,9 +865,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -849,70 +873,46 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1384,40 +1384,40 @@
       </c>
     </row>
     <row r="4" spans="2:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="46" t="s">
+      <c r="E4" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="47"/>
-      <c r="G4" s="46" t="s">
+      <c r="F4" s="55"/>
+      <c r="G4" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="70"/>
-      <c r="I4" s="41" t="s">
+      <c r="H4" s="48"/>
+      <c r="I4" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="65"/>
-      <c r="K4" s="46" t="s">
+      <c r="J4" s="50"/>
+      <c r="K4" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="70"/>
-      <c r="M4" s="64" t="s">
+      <c r="L4" s="48"/>
+      <c r="M4" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="63"/>
+      <c r="N4" s="46"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B5" s="43"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="49"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="57"/>
       <c r="E5" s="12" t="s">
         <v>14</v>
       </c>
@@ -1475,7 +1475,7 @@
       <c r="I6" s="22">
         <v>180</v>
       </c>
-      <c r="J6" s="66">
+      <c r="J6" s="41">
         <v>35</v>
       </c>
       <c r="K6" s="22">
@@ -1486,7 +1486,7 @@
         <f>F6-H6-H6</f>
         <v>821</v>
       </c>
-      <c r="M6" s="68">
+      <c r="M6" s="43">
         <f>E6-H6-H6</f>
         <v>1169</v>
       </c>
@@ -1521,7 +1521,7 @@
       <c r="I7" s="22">
         <v>180</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="41">
         <v>35</v>
       </c>
       <c r="K7" s="22">
@@ -1532,7 +1532,7 @@
         <f t="shared" ref="L7:L11" si="2">F7-H7-H7</f>
         <v>574</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="43">
         <f t="shared" ref="M7:M11" si="3">E7-H7-H7</f>
         <v>821</v>
       </c>
@@ -1567,7 +1567,7 @@
       <c r="I8" s="22">
         <v>180</v>
       </c>
-      <c r="J8" s="66">
+      <c r="J8" s="41">
         <v>35</v>
       </c>
       <c r="K8" s="22">
@@ -1578,7 +1578,7 @@
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
-      <c r="M8" s="68">
+      <c r="M8" s="43">
         <f t="shared" si="3"/>
         <v>574</v>
       </c>
@@ -1613,7 +1613,7 @@
       <c r="I9" s="22">
         <v>180</v>
       </c>
-      <c r="J9" s="66">
+      <c r="J9" s="41">
         <v>35</v>
       </c>
       <c r="K9" s="22">
@@ -1624,7 +1624,7 @@
         <f t="shared" si="2"/>
         <v>287</v>
       </c>
-      <c r="M9" s="68">
+      <c r="M9" s="43">
         <f t="shared" si="3"/>
         <v>410</v>
       </c>
@@ -1659,7 +1659,7 @@
       <c r="I10" s="22">
         <v>180</v>
       </c>
-      <c r="J10" s="66">
+      <c r="J10" s="41">
         <v>35</v>
       </c>
       <c r="K10" s="22">
@@ -1670,7 +1670,7 @@
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="M10" s="68">
+      <c r="M10" s="43">
         <f t="shared" si="3"/>
         <v>287</v>
       </c>
@@ -1705,7 +1705,7 @@
       <c r="I11" s="24">
         <v>180</v>
       </c>
-      <c r="J11" s="67">
+      <c r="J11" s="42">
         <v>35</v>
       </c>
       <c r="K11" s="24">
@@ -1716,7 +1716,7 @@
         <f t="shared" si="2"/>
         <v>138</v>
       </c>
-      <c r="M11" s="69">
+      <c r="M11" s="44">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
@@ -1801,14 +1801,14 @@
     <row r="4" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B4" s="33"/>
       <c r="C4" s="34"/>
-      <c r="D4" s="51">
+      <c r="D4" s="58">
         <v>185</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
       <c r="J4" s="34"/>
     </row>
     <row r="5" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
@@ -1826,15 +1826,15 @@
       <c r="G5" s="35">
         <v>30</v>
       </c>
-      <c r="H5" s="52">
+      <c r="H5" s="60">
         <f>D4-SUM(D5:G5)</f>
         <v>95</v>
       </c>
-      <c r="I5" s="52"/>
+      <c r="I5" s="60"/>
       <c r="J5" s="34"/>
     </row>
     <row r="6" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="51">
+      <c r="B6" s="58">
         <v>36</v>
       </c>
       <c r="C6" s="35">
@@ -1850,14 +1850,14 @@
       <c r="G6" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="53" t="s">
+      <c r="H6" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="I6" s="54"/>
+      <c r="I6" s="63"/>
       <c r="J6" s="34"/>
     </row>
     <row r="7" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="51"/>
+      <c r="B7" s="58"/>
       <c r="C7" s="36">
         <f>C6</f>
         <v>6</v>
@@ -1868,12 +1868,12 @@
       <c r="E7" s="37"/>
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="56"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="66"/>
       <c r="J7" s="34"/>
     </row>
     <row r="8" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="51"/>
+      <c r="B8" s="58"/>
       <c r="C8" s="36">
         <f>C6</f>
         <v>6</v>
@@ -1884,12 +1884,12 @@
       <c r="E8" s="37"/>
       <c r="F8" s="37"/>
       <c r="G8" s="37"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="58"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="69"/>
       <c r="J8" s="34"/>
     </row>
     <row r="9" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="51"/>
+      <c r="B9" s="58"/>
       <c r="C9" s="59">
         <f>B6-SUM(C6:C8)</f>
         <v>18</v>
@@ -1897,12 +1897,12 @@
       <c r="D9" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="53" t="s">
+      <c r="E9" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="63"/>
       <c r="I9" s="38" t="s">
         <v>26</v>
       </c>
@@ -1912,13 +1912,13 @@
       </c>
     </row>
     <row r="10" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="51"/>
+      <c r="B10" s="58"/>
       <c r="C10" s="59"/>
       <c r="D10" s="31"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="56"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="66"/>
       <c r="I10" s="38" t="s">
         <v>27</v>
       </c>
@@ -1928,13 +1928,13 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="51"/>
+      <c r="B11" s="58"/>
       <c r="C11" s="59"/>
       <c r="D11" s="40"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="58"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="69"/>
       <c r="I11" s="38" t="s">
         <v>28</v>
       </c>
@@ -1950,13 +1950,13 @@
         <f>D5</f>
         <v>20</v>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="70">
         <f>D4-I12-D12</f>
         <v>105</v>
       </c>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
       <c r="I12" s="35">
         <v>60</v>
       </c>
@@ -1985,14 +1985,14 @@
     <row r="16" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B16" s="33"/>
       <c r="C16" s="34"/>
-      <c r="D16" s="51">
-        <v>210</v>
-      </c>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
+      <c r="D16" s="58">
+        <v>200</v>
+      </c>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
       <c r="J16" s="34"/>
     </row>
     <row r="17" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
@@ -2010,15 +2010,15 @@
       <c r="G17" s="35">
         <v>30</v>
       </c>
-      <c r="H17" s="52">
+      <c r="H17" s="60">
         <f>D16-SUM(D17:G17)</f>
-        <v>120</v>
-      </c>
-      <c r="I17" s="52"/>
+        <v>110</v>
+      </c>
+      <c r="I17" s="60"/>
       <c r="J17" s="34"/>
     </row>
     <row r="18" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B18" s="51">
+      <c r="B18" s="58">
         <v>36</v>
       </c>
       <c r="C18" s="35">
@@ -2034,14 +2034,14 @@
       <c r="G18" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="53" t="s">
+      <c r="H18" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="54"/>
+      <c r="I18" s="63"/>
       <c r="J18" s="34"/>
     </row>
     <row r="19" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B19" s="51"/>
+      <c r="B19" s="58"/>
       <c r="C19" s="36">
         <f>C18</f>
         <v>6</v>
@@ -2052,12 +2052,12 @@
       <c r="E19" s="37"/>
       <c r="F19" s="37"/>
       <c r="G19" s="37"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="56"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="66"/>
       <c r="J19" s="34"/>
     </row>
     <row r="20" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B20" s="51"/>
+      <c r="B20" s="58"/>
       <c r="C20" s="36">
         <f>C18</f>
         <v>6</v>
@@ -2068,12 +2068,12 @@
       <c r="E20" s="37"/>
       <c r="F20" s="37"/>
       <c r="G20" s="37"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="58"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="69"/>
       <c r="J20" s="34"/>
     </row>
     <row r="21" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B21" s="51"/>
+      <c r="B21" s="58"/>
       <c r="C21" s="59">
         <f>B18-SUM(C18:C20)</f>
         <v>18</v>
@@ -2081,12 +2081,12 @@
       <c r="D21" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="53" t="s">
+      <c r="E21" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="54"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="63"/>
       <c r="I21" s="38" t="s">
         <v>26</v>
       </c>
@@ -2096,13 +2096,13 @@
       </c>
     </row>
     <row r="22" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B22" s="51"/>
+      <c r="B22" s="58"/>
       <c r="C22" s="59"/>
       <c r="D22" s="31"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="56"/>
+      <c r="E22" s="64"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="66"/>
       <c r="I22" s="38" t="s">
         <v>27</v>
       </c>
@@ -2112,13 +2112,13 @@
       </c>
     </row>
     <row r="23" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B23" s="51"/>
+      <c r="B23" s="58"/>
       <c r="C23" s="59"/>
       <c r="D23" s="40"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="58"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="69"/>
       <c r="I23" s="38" t="s">
         <v>28</v>
       </c>
@@ -2134,13 +2134,13 @@
         <f>D17</f>
         <v>20</v>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="70">
         <f>D16-I24-D24</f>
-        <v>130</v>
-      </c>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
+        <v>120</v>
+      </c>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
       <c r="I24" s="35">
         <v>60</v>
       </c>
@@ -2155,19 +2155,13 @@
       <c r="G25" s="34"/>
       <c r="H25" s="34">
         <f>H17-I24</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I25" s="34"/>
       <c r="J25" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B6:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="E9:H11"/>
-    <mergeCell ref="H6:I8"/>
     <mergeCell ref="E12:H12"/>
     <mergeCell ref="E24:H24"/>
     <mergeCell ref="D16:I16"/>
@@ -2176,6 +2170,12 @@
     <mergeCell ref="H18:I20"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="E21:H23"/>
+    <mergeCell ref="B6:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="E9:H11"/>
+    <mergeCell ref="H6:I8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/file/table/DAPC_TamanoPapelNTC1687.xlsx
+++ b/file/table/DAPC_TamanoPapelNTC1687.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED6EE0A-CC28-4A8E-A628-0BCF69F37FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E49368-2D4C-490B-A0FF-D867D4270FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{805D00DC-0F9A-4825-8987-91294E190814}"/>
   </bookViews>
@@ -874,44 +874,44 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1801,14 +1801,14 @@
     <row r="4" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B4" s="33"/>
       <c r="C4" s="34"/>
-      <c r="D4" s="58">
+      <c r="D4" s="59">
         <v>185</v>
       </c>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
       <c r="J4" s="34"/>
     </row>
     <row r="5" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
@@ -1834,7 +1834,7 @@
       <c r="J5" s="34"/>
     </row>
     <row r="6" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="58">
+      <c r="B6" s="59">
         <v>36</v>
       </c>
       <c r="C6" s="35">
@@ -1853,11 +1853,11 @@
       <c r="H6" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="I6" s="63"/>
+      <c r="I6" s="62"/>
       <c r="J6" s="34"/>
     </row>
     <row r="7" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="58"/>
+      <c r="B7" s="59"/>
       <c r="C7" s="36">
         <f>C6</f>
         <v>6</v>
@@ -1868,12 +1868,12 @@
       <c r="E7" s="37"/>
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="66"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="64"/>
       <c r="J7" s="34"/>
     </row>
     <row r="8" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="58"/>
+      <c r="B8" s="59"/>
       <c r="C8" s="36">
         <f>C6</f>
         <v>6</v>
@@ -1884,13 +1884,13 @@
       <c r="E8" s="37"/>
       <c r="F8" s="37"/>
       <c r="G8" s="37"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="69"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="66"/>
       <c r="J8" s="34"/>
     </row>
     <row r="9" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="58"/>
-      <c r="C9" s="59">
+      <c r="B9" s="59"/>
+      <c r="C9" s="67">
         <f>B6-SUM(C6:C8)</f>
         <v>18</v>
       </c>
@@ -1900,9 +1900,9 @@
       <c r="E9" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="63"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="62"/>
       <c r="I9" s="38" t="s">
         <v>26</v>
       </c>
@@ -1912,13 +1912,13 @@
       </c>
     </row>
     <row r="10" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="58"/>
-      <c r="C10" s="59"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="67"/>
       <c r="D10" s="31"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="66"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="64"/>
       <c r="I10" s="38" t="s">
         <v>27</v>
       </c>
@@ -1928,13 +1928,13 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="58"/>
-      <c r="C11" s="59"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="67"/>
       <c r="D11" s="40"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="69"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="66"/>
       <c r="I11" s="38" t="s">
         <v>28</v>
       </c>
@@ -1950,13 +1950,13 @@
         <f>D5</f>
         <v>20</v>
       </c>
-      <c r="E12" s="70">
+      <c r="E12" s="58">
         <f>D4-I12-D12</f>
         <v>105</v>
       </c>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
       <c r="I12" s="35">
         <v>60</v>
       </c>
@@ -1985,14 +1985,14 @@
     <row r="16" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B16" s="33"/>
       <c r="C16" s="34"/>
-      <c r="D16" s="58">
+      <c r="D16" s="59">
         <v>200</v>
       </c>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="59"/>
       <c r="J16" s="34"/>
     </row>
     <row r="17" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
@@ -2018,7 +2018,7 @@
       <c r="J17" s="34"/>
     </row>
     <row r="18" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B18" s="58">
+      <c r="B18" s="59">
         <v>36</v>
       </c>
       <c r="C18" s="35">
@@ -2037,11 +2037,11 @@
       <c r="H18" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="63"/>
+      <c r="I18" s="62"/>
       <c r="J18" s="34"/>
     </row>
     <row r="19" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B19" s="58"/>
+      <c r="B19" s="59"/>
       <c r="C19" s="36">
         <f>C18</f>
         <v>6</v>
@@ -2052,12 +2052,12 @@
       <c r="E19" s="37"/>
       <c r="F19" s="37"/>
       <c r="G19" s="37"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="66"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="64"/>
       <c r="J19" s="34"/>
     </row>
     <row r="20" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B20" s="58"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="36">
         <f>C18</f>
         <v>6</v>
@@ -2068,13 +2068,13 @@
       <c r="E20" s="37"/>
       <c r="F20" s="37"/>
       <c r="G20" s="37"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="69"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="66"/>
       <c r="J20" s="34"/>
     </row>
     <row r="21" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B21" s="58"/>
-      <c r="C21" s="59">
+      <c r="B21" s="59"/>
+      <c r="C21" s="67">
         <f>B18-SUM(C18:C20)</f>
         <v>18</v>
       </c>
@@ -2084,9 +2084,9 @@
       <c r="E21" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="63"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="62"/>
       <c r="I21" s="38" t="s">
         <v>26</v>
       </c>
@@ -2096,13 +2096,13 @@
       </c>
     </row>
     <row r="22" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B22" s="58"/>
-      <c r="C22" s="59"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="67"/>
       <c r="D22" s="31"/>
-      <c r="E22" s="64"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="66"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="64"/>
       <c r="I22" s="38" t="s">
         <v>27</v>
       </c>
@@ -2112,13 +2112,13 @@
       </c>
     </row>
     <row r="23" spans="2:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B23" s="58"/>
-      <c r="C23" s="59"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="67"/>
       <c r="D23" s="40"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="69"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="66"/>
       <c r="I23" s="38" t="s">
         <v>28</v>
       </c>
@@ -2134,13 +2134,13 @@
         <f>D17</f>
         <v>20</v>
       </c>
-      <c r="E24" s="70">
+      <c r="E24" s="58">
         <f>D16-I24-D24</f>
         <v>120</v>
       </c>
-      <c r="F24" s="70"/>
-      <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
       <c r="I24" s="35">
         <v>60</v>
       </c>
@@ -2162,6 +2162,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B6:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="E9:H11"/>
+    <mergeCell ref="H6:I8"/>
     <mergeCell ref="E12:H12"/>
     <mergeCell ref="E24:H24"/>
     <mergeCell ref="D16:I16"/>
@@ -2170,12 +2176,6 @@
     <mergeCell ref="H18:I20"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="E21:H23"/>
-    <mergeCell ref="B6:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="E9:H11"/>
-    <mergeCell ref="H6:I8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
